--- a/artfynd/A 23051-2026 artfynd.xlsx
+++ b/artfynd/A 23051-2026 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>134058030</v>
       </c>
       <c r="B5" t="n">
-        <v>98049</v>
+        <v>98056</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23051-2026 artfynd.xlsx
+++ b/artfynd/A 23051-2026 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120896979</v>
+        <v>120896460</v>
       </c>
       <c r="B2" t="n">
-        <v>56245</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -762,12 +757,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,37 +789,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120896460</v>
+        <v>120894004</v>
       </c>
       <c r="B3" t="n">
-        <v>56252</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -881,12 +871,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,15 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120897000</v>
+        <v>120896517</v>
       </c>
       <c r="B4" t="n">
-        <v>56266</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56837</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,12 +985,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,7 +1020,7 @@
         <v>134058030</v>
       </c>
       <c r="B5" t="n">
-        <v>98056</v>
+        <v>98063</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
